--- a/public/mau-nhap-hang-loat.xlsx
+++ b/public/mau-nhap-hang-loat.xlsx
@@ -12,178 +12,271 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
-  <si>
-    <t>Tên sản phẩm</t>
-  </si>
-  <si>
-    <t>Thương hiệu</t>
-  </si>
-  <si>
-    <t>Nhà cung cấp</t>
-  </si>
-  <si>
-    <t>Mã SP</t>
-  </si>
-  <si>
-    <t>Hạng mục</t>
-  </si>
-  <si>
-    <t>Nhóm</t>
-  </si>
-  <si>
-    <t>Kích thước</t>
-  </si>
-  <si>
-    <t>ĐVT</t>
-  </si>
-  <si>
-    <t>Giá bán lẻ</t>
-  </si>
-  <si>
-    <t>Mô tả</t>
-  </si>
-  <si>
-    <t>Link ảnh</t>
-  </si>
-  <si>
-    <t>Đèn downlight âm trần 12W 4000K</t>
-  </si>
-  <si>
-    <t>SV Lighting</t>
-  </si>
-  <si>
-    <t>DEZ-12W-4000K</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+  <si>
+    <t>THƯƠNG HIỆU</t>
+  </si>
+  <si>
+    <t>NHÀ CUNG CẤP</t>
+  </si>
+  <si>
+    <t>HẠNG MỤC</t>
+  </si>
+  <si>
+    <t>DÒNG SẢN PHẨM</t>
+  </si>
+  <si>
+    <t>TÊN SẢN PHẨM</t>
+  </si>
+  <si>
+    <t>MÃ SẢN PHẨM</t>
+  </si>
+  <si>
+    <t>GIÁ BÁN LẺ</t>
+  </si>
+  <si>
+    <t>CHIẾT KHẤU ĐẠI LÝ (%)</t>
+  </si>
+  <si>
+    <t>CÔNG SUẤT (W)</t>
+  </si>
+  <si>
+    <t>NHIỆT ĐỘ MÀU (K)</t>
+  </si>
+  <si>
+    <t>MÀU SẮC</t>
+  </si>
+  <si>
+    <t>GÓC CHIẾU (°)</t>
+  </si>
+  <si>
+    <t>CHẤT LIỆU</t>
+  </si>
+  <si>
+    <t>CHIỀU CAO (mm)</t>
+  </si>
+  <si>
+    <t>ĐƯỜNG KÍNH (mm)</t>
+  </si>
+  <si>
+    <t>GÓC NGHIÊNG (°)</t>
+  </si>
+  <si>
+    <t>QUANG THÔNG (lm)</t>
+  </si>
+  <si>
+    <t>CHỈ SỐ IP</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
+    <t>HIỆU SUẤT PHÁT QUANG (lm/W)</t>
+  </si>
+  <si>
+    <t>UGR</t>
+  </si>
+  <si>
+    <t>TUỔI THỌ</t>
+  </si>
+  <si>
+    <t>LOẠI CHIP LED</t>
+  </si>
+  <si>
+    <t>SDCM</t>
+  </si>
+  <si>
+    <t>COI</t>
+  </si>
+  <si>
+    <t>BẢO HÀNH (năm)</t>
+  </si>
+  <si>
+    <t>TÊN BỘ NGUỒN</t>
+  </si>
+  <si>
+    <t>MÃ BỘ NGUỒN</t>
+  </si>
+  <si>
+    <t>HÃNG BỘ NGUỒN</t>
+  </si>
+  <si>
+    <t>VỊ TRÍ LẮP NGUỒN</t>
+  </si>
+  <si>
+    <t>TƯƠNG THÍCH ĐIỀU KHIỂN</t>
+  </si>
+  <si>
+    <t>DÒNG RA TỐI ĐA (mA)</t>
+  </si>
+  <si>
+    <t>LẮP NGUỒN RỜI</t>
+  </si>
+  <si>
+    <t>LỖ KHOÉT TRẦN (mm)</t>
+  </si>
+  <si>
+    <t>CẤP BẢO VỆ ĐIỆN</t>
+  </si>
+  <si>
+    <t>NHÓM SẢN PHẨM</t>
+  </si>
+  <si>
+    <t>ĐƠN VỊ TÍNH</t>
+  </si>
+  <si>
+    <t>LINK DATASHEET</t>
+  </si>
+  <si>
+    <t>TRẠNG THÁI</t>
+  </si>
+  <si>
+    <t>GHI CHÚ</t>
+  </si>
+  <si>
+    <t>Osram</t>
+  </si>
+  <si>
+    <t>Sun Light</t>
   </si>
   <si>
     <t>Đèn nội thất</t>
   </si>
   <si>
-    <t>Thiết bị đèn</t>
-  </si>
-  <si>
-    <t>Ø120×H65mm</t>
+    <t>Downlight</t>
+  </si>
+  <si>
+    <t>Đèn downlight âm trần 12W</t>
+  </si>
+  <si>
+    <t>DL-12W-3000</t>
+  </si>
+  <si>
+    <t>Trắng</t>
+  </si>
+  <si>
+    <t>Nhôm đúc</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>IP44</t>
+  </si>
+  <si>
+    <t>Ra90</t>
+  </si>
+  <si>
+    <t>COB</t>
+  </si>
+  <si>
+    <t>Lắp rời</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>Class II</t>
   </si>
   <si>
     <t>Cái</t>
   </si>
   <si>
-    <t>Chip COB, CRI 90+, góc chiếu 36°, quang thông 1080lm</t>
-  </si>
-  <si>
-    <t>https://.../anh.jpg</t>
-  </si>
-  <si>
-    <t>Đèn ốp trần tròn 24W 3000K</t>
-  </si>
-  <si>
-    <t>DEZ-24W-3000K</t>
-  </si>
-  <si>
-    <t>Ø300×H40mm</t>
-  </si>
-  <si>
-    <t>Chip COB, CRI 90+, góc chiếu 120°, 2100lm</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Đèn LED dây 5W/m 3000K</t>
-  </si>
-  <si>
-    <t>Unios</t>
-  </si>
-  <si>
-    <t>LED-5W-3000K</t>
+    <t>Đang kinh doanh</t>
   </si>
   <si>
     <t>Đèn kỹ thuật</t>
   </si>
   <si>
-    <t>8mm</t>
-  </si>
-  <si>
-    <t>Mét</t>
-  </si>
-  <si>
-    <t>LED dây, công suất 5W/m, 3000K</t>
-  </si>
-  <si>
-    <t>CÁCH DÙNG</t>
+    <t>Track light</t>
+  </si>
+  <si>
+    <t>Đèn rọi ray 20W</t>
+  </si>
+  <si>
+    <t>TL-20W-4000</t>
+  </si>
+  <si>
+    <t>Đen</t>
+  </si>
+  <si>
+    <t>Nhôm</t>
+  </si>
+  <si>
+    <t>IP20</t>
+  </si>
+  <si>
+    <t>HƯỚNG DẪN NHẬP HÀNG LOẠT — DEZON QS PRO</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>Điền dữ liệu vào sheet "San pham", mỗi dòng là 1 sản phẩm.</t>
+    <t>Điền vào sheet "San pham"</t>
+  </si>
+  <si>
+    <t>Mỗi dòng = 1 sản phẩm. Cột tiêu đề MÀU XANH là bắt buộc, màu xanh đậm là tuỳ chọn. Xoá 2 dòng ví dụ trước khi nhập thật.</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Chỉ CỘT "Tên sản phẩm" là bắt buộc. Các cột khác điền được thì tốt, để trống cũng được.</t>
+    <t>Giá &amp; chiết khấu</t>
+  </si>
+  <si>
+    <t>GIÁ BÁN LẺ nhập số (vd 208000). Giá đại lý hệ thống tự tính = Giá bán lẻ × (1 − Chiết khấu %).</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Vào app: tab "Nhập dữ liệu" → mục "Nhập hàng loạt từ file" → chọn file này.</t>
+    <t>Cột số</t>
+  </si>
+  <si>
+    <t>Công suất, quang thông, kích thước, góc chiếu… nhập số. Có thể để trống nếu chưa có.</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>Hệ thống tự nhận cột theo tiêu đề (không cần đúng thứ tự). Sau đó tải ảnh cho từng SP rồi bấm nhập.</t>
-  </si>
-  <si>
-    <t>CỘT NHẬN DIỆN</t>
-  </si>
-  <si>
-    <t>Tên gợi ý (có thể dùng tên tương đương)</t>
-  </si>
-  <si>
-    <t>Tên sản phẩm *</t>
-  </si>
-  <si>
-    <t>Tên SP / Name / Product</t>
-  </si>
-  <si>
-    <t>Brand / Hãng</t>
-  </si>
-  <si>
-    <t>NCC / Supplier</t>
-  </si>
-  <si>
-    <t>Mã sản phẩm / Code / SKU</t>
-  </si>
-  <si>
-    <t>Đèn nội thất / ngoại thất / kỹ thuật</t>
-  </si>
-  <si>
-    <t>Ngành hàng / Category</t>
-  </si>
-  <si>
-    <t>Size / Quy cách</t>
-  </si>
-  <si>
-    <t>Đơn vị tính / Unit (Cái/Bộ/Mét)</t>
-  </si>
-  <si>
-    <t>Đơn giá bán / Giá / Price</t>
-  </si>
-  <si>
-    <t>Description / Ghi chú</t>
-  </si>
-  <si>
-    <t>URL ảnh / Image URL</t>
+    <t>Cột chọn</t>
+  </si>
+  <si>
+    <t>HẠNG MỤC: Đèn nội thất / ngoại thất / kỹ thuật. NHIỆT ĐỘ MÀU: 2700/3000/4000/5000/6500. TRẠNG THÁI: Đang kinh doanh / Ngưng / Đặt hàng. LẮP NGUỒN RỜI: Có / Không.</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Ảnh sản phẩm</t>
+  </si>
+  <si>
+    <t>KHÔNG nhập ảnh trong file này. Sau khi tải file lên, hệ thống hiện danh sách để bạn tải ảnh (1 ảnh chính + nhiều ảnh phụ) cho từng SP rồi lưu.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Mã trùng</t>
+  </si>
+  <si>
+    <t>Nếu MÃ SẢN PHẨM đã tồn tại trong DB, dòng đó sẽ CẬP NHẬT (ghi đè) thay vì tạo mới.</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Tải lên</t>
+  </si>
+  <si>
+    <t>Lưu file → vào tab "Nhập dữ liệu" → mục "Nhập hàng loạt từ file" → chọn file này.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -194,18 +287,28 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF334155"/>
+      <sz val="10"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF123350"/>
-      <sz val="12"/>
+      <color rgb="FF12315A"/>
+      <sz val="13"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1E63D2"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <color rgb="FF334155"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,7 +317,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF123350"/>
+        <fgColor rgb="FF1E63D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF12315A"/>
       </patternFill>
     </fill>
   </fills>
@@ -228,32 +336,31 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="FF20406B"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFBFC9D4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -595,21 +702,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
+    <col min="21" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="17" customWidth="1"/>
+    <col min="27" max="27" width="15" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="30" max="30" width="19" customWidth="1"/>
+    <col min="31" max="31" width="25" customWidth="1"/>
+    <col min="32" max="32" width="22" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="34" width="21" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="16" customWidth="1"/>
+    <col min="37" max="37" width="14" customWidth="1"/>
+    <col min="38" max="38" width="17" customWidth="1"/>
+    <col min="39" max="39" width="14" customWidth="1"/>
+    <col min="40" max="40" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,113 +777,340 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="3">
+        <v>208000</v>
+      </c>
+      <c r="H2" s="3">
+        <v>35</v>
+      </c>
+      <c r="I2" s="3">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3">
-        <v>208000</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
+      <c r="J2" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="3">
+        <v>36</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="3">
+        <v>55</v>
+      </c>
+      <c r="O2" s="3">
+        <v>100</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1080</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="3">
+        <v>90</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>90</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="3">
+        <v>460000</v>
+      </c>
+      <c r="H3" s="3">
+        <v>35</v>
+      </c>
+      <c r="I3" s="3">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3">
-        <v>234000</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3">
-        <v>39000</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
+      <c r="M3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -757,155 +1118,100 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
+    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>38</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>42</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>54</v>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/public/mau-nhap-hang-loat.xlsx
+++ b/public/mau-nhap-hang-loat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>THƯƠNG HIỆU</t>
   </si>
@@ -107,6 +107,9 @@
     <t>HÃNG BỘ NGUỒN</t>
   </si>
   <si>
+    <t>GIÁ BÁN BỘ NGUỒN</t>
+  </si>
+  <si>
     <t>VỊ TRÍ LẮP NGUỒN</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
   </si>
   <si>
     <t>COB</t>
+  </si>
+  <si>
+    <t>85000</t>
   </si>
   <si>
     <t>Ø75</t>
@@ -749,7 +755,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AO4"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -759,15 +765,17 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="22" width="13" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="34" width="13" customWidth="1"/>
-    <col min="35" max="35" width="17" customWidth="1"/>
-    <col min="36" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="20" customWidth="1"/>
-    <col min="40" max="40" width="13" customWidth="1"/>
-    <col min="41" max="41" width="22" customWidth="1"/>
+    <col min="24" max="30" width="13" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
+    <col min="32" max="35" width="13" customWidth="1"/>
+    <col min="36" max="36" width="17" customWidth="1"/>
+    <col min="37" max="39" width="13" customWidth="1"/>
+    <col min="40" max="40" width="20" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="42" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,19 +878,19 @@
       <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="2" t="s">
@@ -891,25 +899,28 @@
       <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3">
         <v>208000</v>
@@ -918,19 +929,19 @@
         <v>35</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3">
         <v>3000</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" s="3">
         <v>24</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
@@ -941,19 +952,19 @@
         <v>1080</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -963,42 +974,45 @@
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
+      <c r="AE2" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
-      <c r="AI2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="AK2" s="3"/>
-      <c r="AL2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO2" s="3"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP2" s="3"/>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" s="3">
         <v>1285000</v>
@@ -1007,19 +1021,19 @@
         <v>35</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J3" s="3">
         <v>3000</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L3" s="3">
         <v>360</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -1028,16 +1042,16 @@
         <v>158</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -1048,42 +1062,43 @@
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
+      <c r="AE3" s="4"/>
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
-      <c r="AI3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="AK3" s="3"/>
-      <c r="AL3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO3" s="3"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP3" s="3"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3">
         <v>1285000</v>
@@ -1092,19 +1107,19 @@
         <v>35</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J4" s="3">
         <v>4000</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4" s="3">
         <v>360</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1113,16 +1128,16 @@
         <v>158</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -1133,23 +1148,24 @@
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
+      <c r="AE4" s="4"/>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
-      <c r="AI4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="AK4" s="3"/>
-      <c r="AL4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM4" s="3"/>
-      <c r="AN4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,119 +1187,119 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
